--- a/GourmetProject/GameConfig/Datas/stomach_fragment.xlsx
+++ b/GourmetProject/GameConfig/Datas/stomach_fragment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,72 +456,96 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>##comment</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>胃碎片ID</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>出现隐藏分下限</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>出现隐藏分上限</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>随机基础权重</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>商店价格</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>碎片形状行列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>list,string</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>gut_4x4</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>XXXX</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>gut_4x4</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>XXXX</t>
@@ -556,26 +580,14 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>frag_1x2</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>10</v>
-      </c>
-      <c r="E7" t="n">
-        <v>100</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2</v>
-      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>XXXX</t>
         </is>
       </c>
     </row>
@@ -583,7 +595,7 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>frag_2x1</t>
+          <t>frag_1x2</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -600,17 +612,29 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>XX</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>frag_2x1</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>X</t>
@@ -619,75 +643,88 @@
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>frag_L</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>10</v>
-      </c>
-      <c r="D10" t="n">
-        <v>25</v>
-      </c>
-      <c r="E10" t="n">
-        <v>70</v>
-      </c>
-      <c r="F10" t="n">
-        <v>4</v>
-      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>X</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>frag_L</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E11" t="n">
+        <v>70</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4</v>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>.X</t>
+          <t>XX</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>frag_gold2x2</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>25</v>
-      </c>
-      <c r="D12" t="n">
-        <v>45</v>
-      </c>
-      <c r="E12" t="n">
-        <v>40</v>
-      </c>
-      <c r="F12" t="n">
-        <v>6</v>
-      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>.X</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>frag_gold2x2</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>25</v>
+      </c>
+      <c r="D13" t="n">
+        <v>45</v>
+      </c>
+      <c r="E13" t="n">
+        <v>40</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6</v>
+      </c>
       <c r="G13" t="inlineStr">
+        <is>
+          <t>XX</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
         <is>
           <t>XX</t>
         </is>
